--- a/DataTables/DetailText/剧情/000_07名望过低.xlsx
+++ b/DataTables/DetailText/剧情/000_07名望过低.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D0BBD0-959F-4C38-95A4-47CA9893180E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64AD7A19-078D-442D-9763-68B2807C82BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -204,9 +204,6 @@
     <t>≤</t>
   </si>
   <si>
-    <t>end_game</t>
-  </si>
-  <si>
     <t>李东璧，有人告你医术不精，招摇撞骗，跟我们去衙门走一趟吧。</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -239,6 +236,9 @@
   <si>
     <t>000_07</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>endgame</t>
   </si>
 </sst>
 </file>
@@ -819,7 +819,7 @@
     </row>
     <row r="2" spans="1:20" s="20" customFormat="1" ht="18">
       <c r="A2" s="24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>16</v>
@@ -840,7 +840,7 @@
       <c r="J2" s="21"/>
       <c r="K2" s="22"/>
       <c r="L2" s="22" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M2" s="21"/>
       <c r="N2" s="22"/>
@@ -925,7 +925,7 @@
       <formula1>"≥,≤"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="L2" xr:uid="{8F3B19E4-5443-4A64-8AB7-8B442641C9DA}">
-      <formula1>"clinic,night,end_game"</formula1>
+      <formula1>"clinic,night,endgame"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="S2" xr:uid="{BDA159CC-8168-4340-A03C-531FFE93E69A}">
       <formula1>"TRUE,FALSE"</formula1>
@@ -999,7 +999,7 @@
         <v>15</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1054,7 +1054,7 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H5" s="12" t="s">
         <v>21</v>

--- a/DataTables/DetailText/剧情/000_07名望过低.xlsx
+++ b/DataTables/DetailText/剧情/000_07名望过低.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64AD7A19-078D-442D-9763-68B2807C82BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A4B1DA-E706-4E7A-83D5-0C7BDFFE92EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13950" yWindow="3360" windowWidth="12060" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -20,17 +20,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -225,7 +214,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="游ゴシック"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -238,7 +227,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>endgame</t>
+    <t>gameover</t>
   </si>
 </sst>
 </file>
@@ -249,7 +238,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +252,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -284,7 +273,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -459,7 +448,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -738,24 +727,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1328125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.1328125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.265625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="20" customFormat="1" ht="18">
+    <row r="1" spans="1:20" s="20" customFormat="1">
       <c r="A1" s="13" t="s">
         <v>22</v>
       </c>
@@ -817,7 +806,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="20" customFormat="1" ht="18">
+    <row r="2" spans="1:20" s="20" customFormat="1">
       <c r="A2" s="24" t="s">
         <v>43</v>
       </c>
@@ -924,14 +913,14 @@
     <dataValidation type="list" sqref="E2 G2" xr:uid="{E1DAEE95-F9FD-4487-BC68-F028728397C2}">
       <formula1>"≥,≤"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="L2" xr:uid="{8F3B19E4-5443-4A64-8AB7-8B442641C9DA}">
-      <formula1>"clinic,night,endgame"</formula1>
-    </dataValidation>
     <dataValidation type="list" sqref="S2" xr:uid="{BDA159CC-8168-4340-A03C-531FFE93E69A}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="K2" xr:uid="{1E95ACD4-DBD3-4851-BD2C-1C531EF559AD}">
       <formula1>"cured,failed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="L2" xr:uid="{3FAE70C2-03A7-49C5-ACA8-C0BBCFFF1C9E}">
+      <formula1>"clinic,night,gameover,endgame"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -943,14 +932,14 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1042,7 +1031,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18.75">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>

--- a/DataTables/DetailText/剧情/000_07名望过低.xlsx
+++ b/DataTables/DetailText/剧情/000_07名望过低.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A4B1DA-E706-4E7A-83D5-0C7BDFFE92EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D5DF915-3E9F-450C-9D33-7DC3F492C8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13950" yWindow="3360" windowWidth="12060" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3780" yWindow="6840" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="46">
   <si>
     <t>LineIndex</t>
   </si>
@@ -214,7 +225,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
+        <rFont val="游ゴシック"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -228,6 +239,10 @@
   </si>
   <si>
     <t>gameover</t>
+  </si>
+  <si>
+    <t>Music</t>
+    <phoneticPr fontId="8"/>
   </si>
 </sst>
 </file>
@@ -238,7 +253,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -252,7 +267,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -273,7 +288,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -376,7 +391,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -446,9 +461,12 @@
     <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -727,24 +745,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="7.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="8.86328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.86328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.59765625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.1328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.86328125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.265625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="20" customFormat="1">
+    <row r="1" spans="1:20" s="20" customFormat="1" ht="18">
       <c r="A1" s="13" t="s">
         <v>22</v>
       </c>
@@ -806,7 +824,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="20" customFormat="1">
+    <row r="2" spans="1:20" s="20" customFormat="1" ht="18">
       <c r="A2" s="24" t="s">
         <v>43</v>
       </c>
@@ -929,21 +947,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -968,8 +986,11 @@
       <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -990,8 +1011,9 @@
       <c r="H2" s="12" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1010,8 +1032,9 @@
       <c r="H3" s="12" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1030,8 +1053,9 @@
       <c r="H4" s="12" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9" ht="18.75">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1048,8 +1072,9 @@
       <c r="H5" s="12" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1060,8 +1085,9 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="1"/>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1072,6 +1098,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/000_07名望过低.xlsx
+++ b/DataTables/DetailText/剧情/000_07名望过低.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D5DF915-3E9F-450C-9D33-7DC3F492C8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889C570A-5F54-45AC-BC12-D381A4971C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3780" yWindow="6840" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -20,17 +20,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -206,6 +195,17 @@
   <si>
     <t>李东璧，有人告你医术不精，招摇撞骗，跟我们去衙门走一趟吧。</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>000_07</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>gameover</t>
+  </si>
+  <si>
+    <t>Music</t>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <r>
@@ -225,24 +225,13 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="游ゴシック"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>/002.png</t>
+      <t>/000_02.png</t>
     </r>
     <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>000_07</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>gameover</t>
-  </si>
-  <si>
-    <t>Music</t>
-    <phoneticPr fontId="8"/>
   </si>
 </sst>
 </file>
@@ -253,7 +242,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -267,7 +256,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -288,7 +277,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -466,7 +455,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -745,24 +734,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1328125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.1328125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.265625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="20" customFormat="1" ht="18">
+    <row r="1" spans="1:20" s="20" customFormat="1">
       <c r="A1" s="13" t="s">
         <v>22</v>
       </c>
@@ -824,9 +813,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="20" customFormat="1" ht="18">
+    <row r="2" spans="1:20" s="20" customFormat="1">
       <c r="A2" s="24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>16</v>
@@ -847,7 +836,7 @@
       <c r="J2" s="21"/>
       <c r="K2" s="22"/>
       <c r="L2" s="22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M2" s="21"/>
       <c r="N2" s="22"/>
@@ -950,14 +939,14 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -987,7 +976,7 @@
         <v>4</v>
       </c>
       <c r="I1" s="25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1055,7 +1044,7 @@
       </c>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" ht="18.75">
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1066,8 +1055,8 @@
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
-      <c r="G5" t="s">
-        <v>42</v>
+      <c r="G5" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="H5" s="12" t="s">
         <v>21</v>
